--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LIVE (official sources) + SEED fallback for un-fetched series</t>
+          <t>SEED (illustrative; run etl/fetch.py for live data)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SEED (illustrative; run etl/fetch.py for live data)</t>
+          <t>LIVE (official sources) + SEED fallback for un-fetched series</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -53846,7 +53846,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Central-bank absorption of the market; higher share = thinner free float</t>
+          <t>Central-bank absorption of the market; higher share = thinner free float, worse market liquidity (polarity -1).</t>
         </is>
       </c>
     </row>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LIVE (official sources) + SEED fallback for un-fetched series</t>
+          <t>SEED (illustrative; run etl/fetch.py for live data)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -54467,7 +54467,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Lending by domestic commercial banks (avg amounts outstanding) y/y. IR04 carries the interest rate on loans outstanding, not the amount, so this stays seeded with verified BoJ prints pinned until the amounts-outstanding database is identified.</t>
+          <t>BoJ MD11 carries the loan amounts (IR04 has only the rate charged on them) but publishes no ready-made y/y series and holds ~80 near-identical variants by borrower, account and bank group under an opaque DL prefix. The resolver refuses to guess between them, so this stays seeded with verified BoJ prints pinned (Jul-2026 +5.9%, Aug-2026 +5.8%, banks excl. shinkin). To finish: identify the exact series in the Data Search browser and add its code to sources.BOJ_API_SERIES.</t>
         </is>
       </c>
     </row>

--- a/Japan_ML_Tracker.xlsx
+++ b/Japan_ML_Tracker.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>+0.14  Broadly neutral</t>
+          <t>+0.15  Broadly neutral</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Monetary conditions score +0.46 (mildly accommodative) and liquidity conditions -0.17 (mildly restrictive); the combined index is +0.14 (broadly neutral), each measured against the longest available history of its indicators (+ = easier / more liquid). Money growth is subdued (M2 +2.2% y/y) and the BoJ balance sheet is contracting (-8.2% y/y; monetary base -13.1%), while the yen remains weak in real effective terms (REER 64, 2020=100) — the quantity of money is tightening even as the exchange-rate channel stays easy. Funding liquidity is orderly (3m TIBOR-OIS 0.19pp; USD/JPY basis -30bp) and JGB market functioning is recovering (DI -14) as the BoJ's JGB share falls to 49%.</t>
+          <t>Monetary conditions score +0.46 (mildly accommodative) and liquidity conditions -0.17 (mildly restrictive); the combined index is +0.15 (broadly neutral), each measured against the longest available history of its indicators (+ = easier / more liquid). Money growth is subdued (M2 +2.2% y/y) and the BoJ balance sheet is contracting (-8.2% y/y; monetary base -13.1%), while the yen remains weak in real effective terms (REER 64, 2020=100) — the quantity of money is tightening even as the exchange-rate channel stays easy. Funding liquidity is orderly (3m TIBOR-OIS 0.19pp; USD/JPY basis -30bp) and JGB market functioning is recovering (DI -14) as the BoJ's JGB share falls to 49%.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10.196</v>
+        <v>10.205</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.086</v>
+        <v>1.085</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-0.93</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="14">
@@ -34435,10 +34435,10 @@
         <v>0.0141</v>
       </c>
       <c r="G634" t="n">
-        <v>1.0864</v>
+        <v>1.085</v>
       </c>
       <c r="H634" t="n">
-        <v>10.1965</v>
+        <v>10.2049</v>
       </c>
       <c r="I634" t="n">
         <v>1.2932</v>
@@ -37181,7 +37181,7 @@
         <v>-1.4179</v>
       </c>
       <c r="C167" t="n">
-        <v>-3.1729</v>
+        <v>-3.1728</v>
       </c>
       <c r="D167" t="n">
         <v>-2.2954</v>
@@ -37190,13 +37190,13 @@
         <v>-1.4179</v>
       </c>
       <c r="F167" t="n">
-        <v>-3.1729</v>
+        <v>-3.1728</v>
       </c>
       <c r="G167" t="n">
         <v>-1.4179</v>
       </c>
       <c r="M167" t="n">
-        <v>-3.1729</v>
+        <v>-3.1728</v>
       </c>
     </row>
     <row r="168">
@@ -37825,7 +37825,7 @@
         <v>-0.8606</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.3754</v>
+        <v>-0.3753</v>
       </c>
       <c r="D190" t="n">
         <v>-0.618</v>
@@ -37834,13 +37834,13 @@
         <v>-0.8606</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.3754</v>
+        <v>-0.3753</v>
       </c>
       <c r="G190" t="n">
         <v>-0.8606</v>
       </c>
       <c r="M190" t="n">
-        <v>-0.3754</v>
+        <v>-0.3753</v>
       </c>
     </row>
     <row r="191">
@@ -38584,7 +38584,7 @@
         <v>-0.0901</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.7632</v>
+        <v>-0.7631</v>
       </c>
       <c r="E217" t="n">
         <v>-1.4362</v>
@@ -40625,7 +40625,7 @@
         <v>0.9968</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.1246</v>
+        <v>-0.1245</v>
       </c>
       <c r="D290" t="n">
         <v>0.4361</v>
@@ -40634,13 +40634,13 @@
         <v>0.9968</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.1246</v>
+        <v>-0.1245</v>
       </c>
       <c r="G290" t="n">
         <v>0.9968</v>
       </c>
       <c r="M290" t="n">
-        <v>-0.1246</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="291">
@@ -41577,7 +41577,7 @@
         <v>-0.1752</v>
       </c>
       <c r="C324" t="n">
-        <v>0.2113</v>
+        <v>0.2112</v>
       </c>
       <c r="D324" t="n">
         <v>0.018</v>
@@ -41586,13 +41586,13 @@
         <v>-0.1752</v>
       </c>
       <c r="F324" t="n">
-        <v>0.2113</v>
+        <v>0.2112</v>
       </c>
       <c r="G324" t="n">
         <v>-0.1752</v>
       </c>
       <c r="M324" t="n">
-        <v>0.2113</v>
+        <v>0.2112</v>
       </c>
     </row>
     <row r="325">
@@ -41605,7 +41605,7 @@
         <v>-0.1799</v>
       </c>
       <c r="C325" t="n">
-        <v>0.1911</v>
+        <v>0.191</v>
       </c>
       <c r="D325" t="n">
         <v>0.0056</v>
@@ -41614,13 +41614,13 @@
         <v>-0.1799</v>
       </c>
       <c r="F325" t="n">
-        <v>0.1911</v>
+        <v>0.191</v>
       </c>
       <c r="G325" t="n">
         <v>-0.1799</v>
       </c>
       <c r="M325" t="n">
-        <v>0.1911</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="326">
@@ -41857,7 +41857,7 @@
         <v>-0.1192</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.1151</v>
+        <v>-0.1152</v>
       </c>
       <c r="D334" t="n">
         <v>-0.1172</v>
@@ -41866,13 +41866,13 @@
         <v>-0.1192</v>
       </c>
       <c r="F334" t="n">
-        <v>-0.1151</v>
+        <v>-0.1152</v>
       </c>
       <c r="G334" t="n">
         <v>-0.1192</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.1151</v>
+        <v>-0.1152</v>
       </c>
     </row>
     <row r="335">
@@ -41969,7 +41969,7 @@
         <v>-0.1235</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.2462</v>
+        <v>-0.2463</v>
       </c>
       <c r="D338" t="n">
         <v>-0.1849</v>
@@ -41978,13 +41978,13 @@
         <v>-0.1235</v>
       </c>
       <c r="F338" t="n">
-        <v>-0.2462</v>
+        <v>-0.2463</v>
       </c>
       <c r="G338" t="n">
         <v>-0.1235</v>
       </c>
       <c r="M338" t="n">
-        <v>-0.2462</v>
+        <v>-0.2463</v>
       </c>
     </row>
     <row r="339">
@@ -42277,7 +42277,7 @@
         <v>-0.07149999999999999</v>
       </c>
       <c r="C349" t="n">
-        <v>0.5081</v>
+        <v>0.508</v>
       </c>
       <c r="D349" t="n">
         <v>0.2183</v>
@@ -42286,13 +42286,13 @@
         <v>-0.07149999999999999</v>
       </c>
       <c r="F349" t="n">
-        <v>0.5081</v>
+        <v>0.508</v>
       </c>
       <c r="G349" t="n">
         <v>-0.07149999999999999</v>
       </c>
       <c r="M349" t="n">
-        <v>0.5081</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="350">
@@ -42765,16 +42765,16 @@
         <v>-0.4434</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.2346</v>
+        <v>-0.2347</v>
       </c>
       <c r="D366" t="n">
-        <v>-0.339</v>
+        <v>-0.3391</v>
       </c>
       <c r="E366" t="n">
         <v>-0.4434</v>
       </c>
       <c r="F366" t="n">
-        <v>-0.2346</v>
+        <v>-0.2347</v>
       </c>
       <c r="G366" t="n">
         <v>0.1179</v>
@@ -42783,7 +42783,7 @@
         <v>-1.0047</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.2346</v>
+        <v>-0.2347</v>
       </c>
     </row>
     <row r="367">
@@ -43086,7 +43086,7 @@
         <v>1.0318</v>
       </c>
       <c r="M375" t="n">
-        <v>0.8173</v>
+        <v>0.8172</v>
       </c>
     </row>
     <row r="376">
@@ -44174,7 +44174,7 @@
         <v>-0.7692</v>
       </c>
       <c r="C401" t="n">
-        <v>-0.6983</v>
+        <v>-0.6984</v>
       </c>
       <c r="D401" t="n">
         <v>-0.7338</v>
@@ -44183,7 +44183,7 @@
         <v>-0.7692</v>
       </c>
       <c r="F401" t="n">
-        <v>-0.6983</v>
+        <v>-0.6984</v>
       </c>
       <c r="G401" t="n">
         <v>-0.0479</v>
@@ -44849,7 +44849,7 @@
         <v>-2.7731</v>
       </c>
       <c r="M416" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.672</v>
       </c>
     </row>
     <row r="417">
@@ -45322,7 +45322,7 @@
         <v>-0.4667</v>
       </c>
       <c r="M427" t="n">
-        <v>0.6269</v>
+        <v>0.6268</v>
       </c>
     </row>
     <row r="428">
@@ -45580,7 +45580,7 @@
         <v>-0.1139</v>
       </c>
       <c r="M433" t="n">
-        <v>0.5112</v>
+        <v>0.5111</v>
       </c>
     </row>
     <row r="434">
@@ -46053,7 +46053,7 @@
         <v>0.2379</v>
       </c>
       <c r="M444" t="n">
-        <v>0.2898</v>
+        <v>0.2897</v>
       </c>
     </row>
     <row r="445">
@@ -46410,7 +46410,7 @@
         <v>-0.3322</v>
       </c>
       <c r="C453" t="n">
-        <v>0.2504</v>
+        <v>0.2503</v>
       </c>
       <c r="D453" t="n">
         <v>-0.0409</v>
@@ -46419,7 +46419,7 @@
         <v>-0.3322</v>
       </c>
       <c r="F453" t="n">
-        <v>0.2504</v>
+        <v>0.2503</v>
       </c>
       <c r="G453" t="n">
         <v>0.3187</v>
@@ -46483,7 +46483,7 @@
         <v>0.2323</v>
       </c>
       <c r="M454" t="n">
-        <v>0.2555</v>
+        <v>0.2554</v>
       </c>
     </row>
     <row r="455">
@@ -46926,7 +46926,7 @@
         <v>-0.4822</v>
       </c>
       <c r="C465" t="n">
-        <v>0.3576</v>
+        <v>0.3575</v>
       </c>
       <c r="D465" t="n">
         <v>-0.0623</v>
@@ -46935,7 +46935,7 @@
         <v>-0.4822</v>
       </c>
       <c r="F465" t="n">
-        <v>0.3576</v>
+        <v>0.3575</v>
       </c>
       <c r="G465" t="n">
         <v>0.1263</v>
@@ -46956,7 +46956,7 @@
         <v>0.4497</v>
       </c>
       <c r="M465" t="n">
-        <v>0.3815</v>
+        <v>0.3814</v>
       </c>
     </row>
     <row r="466">
@@ -47300,7 +47300,7 @@
         <v>0.6629</v>
       </c>
       <c r="M473" t="n">
-        <v>0.4932</v>
+        <v>0.4931</v>
       </c>
     </row>
     <row r="474">
@@ -47601,7 +47601,7 @@
         <v>0.5778</v>
       </c>
       <c r="M480" t="n">
-        <v>0.2489</v>
+        <v>0.2488</v>
       </c>
     </row>
     <row r="481">
@@ -48074,7 +48074,7 @@
         <v>0.595</v>
       </c>
       <c r="M491" t="n">
-        <v>0.2428</v>
+        <v>0.2427</v>
       </c>
     </row>
     <row r="492">
@@ -49579,7 +49579,7 @@
         <v>0.1552</v>
       </c>
       <c r="M526" t="n">
-        <v>0.3704</v>
+        <v>0.3703</v>
       </c>
     </row>
     <row r="527">
@@ -50627,7 +50627,7 @@
         <v>-0.3965</v>
       </c>
       <c r="D551" t="n">
-        <v>-0.0727</v>
+        <v>-0.0726</v>
       </c>
       <c r="E551" t="n">
         <v>0.2512</v>
@@ -52331,7 +52331,7 @@
         <v>0.4095</v>
       </c>
       <c r="M590" t="n">
-        <v>-1.0744</v>
+        <v>-1.0745</v>
       </c>
     </row>
     <row r="591">
@@ -52516,7 +52516,7 @@
         <v>0.6614</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.3412</v>
+        <v>-0.3413</v>
       </c>
       <c r="D595" t="n">
         <v>0.1601</v>
@@ -52525,7 +52525,7 @@
         <v>0.6614</v>
       </c>
       <c r="F595" t="n">
-        <v>-0.3412</v>
+        <v>-0.3413</v>
       </c>
       <c r="G595" t="n">
         <v>1.8228</v>
@@ -54193,16 +54193,16 @@
         <v>0.4602</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.1703</v>
+        <v>-0.1701</v>
       </c>
       <c r="D634" t="n">
-        <v>0.145</v>
+        <v>0.1451</v>
       </c>
       <c r="E634" t="n">
         <v>0.4602</v>
       </c>
       <c r="F634" t="n">
-        <v>-0.1703</v>
+        <v>-0.1701</v>
       </c>
       <c r="G634" t="n">
         <v>0.5974</v>
@@ -54223,7 +54223,7 @@
         <v>0.4206</v>
       </c>
       <c r="M634" t="n">
-        <v>0.3977</v>
+        <v>0.3983</v>
       </c>
     </row>
   </sheetData>
